--- a/artfynd/A 67507-2021 artfynd.xlsx
+++ b/artfynd/A 67507-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 67507-2021 artfynd.xlsx
+++ b/artfynd/A 67507-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>100409461</v>
+        <v>100409445</v>
       </c>
       <c r="B2" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rödjan, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>428998.7015637982</v>
+        <v>428921</v>
       </c>
       <c r="R2" t="n">
-        <v>6507156.016610901</v>
+        <v>6507358</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,19 +743,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>100409445</v>
+        <v>100409461</v>
       </c>
       <c r="B3" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,34 +787,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1339</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rödjan, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>428921.1651917436</v>
+        <v>428998</v>
       </c>
       <c r="R3" t="n">
-        <v>6507358.06330662</v>
+        <v>6507156</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,19 +849,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 67507-2021 artfynd.xlsx
+++ b/artfynd/A 67507-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100409445</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,8 +889,17 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100409461</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>